--- a/artfynd/A 13441-2025 artfynd.xlsx
+++ b/artfynd/A 13441-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124662316</v>
+        <v>124662148</v>
       </c>
       <c r="B2" t="n">
-        <v>90977</v>
+        <v>96354</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124662148</v>
+        <v>124662316</v>
       </c>
       <c r="B3" t="n">
-        <v>96354</v>
+        <v>90977</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>

--- a/artfynd/A 13441-2025 artfynd.xlsx
+++ b/artfynd/A 13441-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124662148</v>
+        <v>124662316</v>
       </c>
       <c r="B2" t="n">
-        <v>96354</v>
+        <v>90977</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124662316</v>
+        <v>124662148</v>
       </c>
       <c r="B3" t="n">
-        <v>90977</v>
+        <v>96354</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>

--- a/artfynd/A 13441-2025 artfynd.xlsx
+++ b/artfynd/A 13441-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124662148</v>
+        <v>124662316</v>
       </c>
       <c r="B2" t="n">
-        <v>96354</v>
+        <v>91131</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124662316</v>
+        <v>124662148</v>
       </c>
       <c r="B3" t="n">
-        <v>90977</v>
+        <v>96522</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>

--- a/artfynd/A 13441-2025 artfynd.xlsx
+++ b/artfynd/A 13441-2025 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>126721326</v>
       </c>
       <c r="B4" t="n">
-        <v>98265</v>
+        <v>98340</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>126721333</v>
       </c>
       <c r="B5" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 13441-2025 artfynd.xlsx
+++ b/artfynd/A 13441-2025 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>126721326</v>
       </c>
       <c r="B4" t="n">
-        <v>98340</v>
+        <v>98346</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>126721333</v>
       </c>
       <c r="B5" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 13441-2025 artfynd.xlsx
+++ b/artfynd/A 13441-2025 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>126721326</v>
       </c>
       <c r="B4" t="n">
-        <v>98346</v>
+        <v>98347</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>126721333</v>
       </c>
       <c r="B5" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 13441-2025 artfynd.xlsx
+++ b/artfynd/A 13441-2025 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>126721326</v>
       </c>
       <c r="B4" t="n">
-        <v>98347</v>
+        <v>98340</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>126721333</v>
       </c>
       <c r="B5" t="n">
-        <v>98443</v>
+        <v>98436</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 13441-2025 artfynd.xlsx
+++ b/artfynd/A 13441-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124662316</v>
+        <v>124662148</v>
       </c>
       <c r="B2" t="n">
-        <v>91131</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -787,37 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124662148</v>
+        <v>124662316</v>
       </c>
       <c r="B3" t="n">
-        <v>96522</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -899,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126721326</v>
+        <v>126721325</v>
       </c>
       <c r="B4" t="n">
-        <v>98347</v>
+        <v>99035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220093</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>632747</v>
+        <v>632753</v>
       </c>
       <c r="R4" t="n">
-        <v>6898868</v>
+        <v>6898803</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,32 +986,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126721333</v>
+        <v>126721326</v>
       </c>
       <c r="B5" t="n">
-        <v>98443</v>
+        <v>99022</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>220093</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>632719</v>
+        <v>632747</v>
       </c>
       <c r="R5" t="n">
-        <v>6898856</v>
+        <v>6898868</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,12 +1051,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1090,6 +1080,103 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>126721333</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Björkön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>632719</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6898856</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-07-16</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-07-16</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 13441-2025 artfynd.xlsx
+++ b/artfynd/A 13441-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124662148</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124662316</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,6 +998,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126721325</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126721326</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,8 +1202,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126721333</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>